--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-28.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-28.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261026" sheetId="1" r:id="R10cc28522d324842"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261026" sheetId="1" r:id="Rdce32028e8d64be9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-28.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-28.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261026" sheetId="1" r:id="Rdce32028e8d64be9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261026" sheetId="1" r:id="Rb48a0cac4c7e4998"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-28.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-28.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261026" sheetId="1" r:id="Rb48a0cac4c7e4998"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261027" sheetId="1" r:id="R2fab8843fdfb41b9"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="173">
-  <x:si>
-    <x:t>Daily Holdings (%)  10/26/2026</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="174">
+  <x:si>
+    <x:t>Daily Holdings (%)  10/27/2026</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -52,19 +52,19 @@
     <x:t>BBG000BBJQV0</x:t>
   </x:si>
   <x:si>
-    <x:t>65,684,206</x:t>
+    <x:t>65,735,754</x:t>
   </x:si>
   <x:si>
     <x:t>Stock</x:t>
   </x:si>
   <x:si>
-    <x:t>$14,187,788,496.00</x:t>
+    <x:t>$14,326,450,226.76</x:t>
   </x:si>
   <x:si>
     <x:t> -- </x:t>
   </x:si>
   <x:si>
-    <x:t>20.57%</x:t>
+    <x:t>20.15%</x:t>
   </x:si>
   <x:si>
     <x:t>TSM</x:t>
@@ -76,13 +76,31 @@
     <x:t>BBG000BD8ZK0</x:t>
   </x:si>
   <x:si>
-    <x:t>15,695,108</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$6,660,532,981.96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.66%</x:t>
+    <x:t>15,707,426</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$6,862,103,196.62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.65%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Advanced Micro Devices Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BBQCY0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7,053,966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,952,054,991.16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.56%</x:t>
   </x:si>
   <x:si>
     <x:t>AVGO</x:t>
@@ -94,13 +112,13 @@
     <x:t>BBG00KHY5S69</x:t>
   </x:si>
   <x:si>
-    <x:t>11,461,460</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,772,768,788.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.47%</x:t>
+    <x:t>11,470,474</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,926,687,364.42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.52%</x:t>
   </x:si>
   <x:si>
     <x:t>TXN</x:t>
@@ -112,31 +130,31 @@
     <x:t>BBG000BVV7G1</x:t>
   </x:si>
   <x:si>
-    <x:t>12,608,355</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,758,802,792.60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.45%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Advanced Micro Devices Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BBQCY0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7,048,434</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,744,692,015.52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.43%</x:t>
+    <x:t>12,618,271</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,897,910,094.61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.48%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Analog Devices Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BB6G37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7,914,906</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,366,605,267.10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.73%</x:t>
   </x:si>
   <x:si>
     <x:t>MU</x:t>
@@ -148,28 +166,13 @@
     <x:t>BBG000C5Z1S3</x:t>
   </x:si>
   <x:si>
-    <x:t>3,573,638</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,229,496,660.60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.68%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Analog Devices Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BB6G37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7,908,686</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,226,190,279.98</x:t>
+    <x:t>3,576,442</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,321,656,271.92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.67%</x:t>
   </x:si>
   <x:si>
     <x:t>MRVL</x:t>
@@ -181,13 +184,13 @@
     <x:t>BBG00ZXBJ153</x:t>
   </x:si>
   <x:si>
-    <x:t>13,104,515</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,063,573,516.70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.44%</x:t>
+    <x:t>13,114,799</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,194,371,592.43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.49%</x:t>
   </x:si>
   <x:si>
     <x:t>ASML</x:t>
@@ -199,15 +202,33 @@
     <x:t>BBG000K6MRN4</x:t>
   </x:si>
   <x:si>
-    <x:t>1,911,279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,036,625,419.51</x:t>
+    <x:t>1,912,779</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,128,483,949.03</x:t>
   </x:si>
   <x:si>
     <x:t>4.40%</x:t>
   </x:si>
   <x:si>
+    <x:t>INTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Intel Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000C0G1D1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31,069,305</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,912,436,650.70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.10%</x:t>
+  </x:si>
+  <x:si>
     <x:t>QCOM</x:t>
   </x:si>
   <x:si>
@@ -217,31 +238,13 @@
     <x:t>BBG000CGC1X8</x:t>
   </x:si>
   <x:si>
-    <x:t>15,656,259</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,811,864,116.40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.08%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Intel Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000C0G1D1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31,044,887</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,808,630,926.89</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.07%</x:t>
+    <x:t>15,668,573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,885,681,089.41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.06%</x:t>
   </x:si>
   <x:si>
     <x:t>AMAT</x:t>
@@ -253,13 +256,13 @@
     <x:t>BBG000BBPFB9</x:t>
   </x:si>
   <x:si>
-    <x:t>7,034,728</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,726,590,225.52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.95%</x:t>
+    <x:t>7,040,262</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,787,450,933.66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.92%</x:t>
   </x:si>
   <x:si>
     <x:t>KLAC</x:t>
@@ -271,10 +274,10 @@
     <x:t>BBG000BMTFR4</x:t>
   </x:si>
   <x:si>
-    <x:t>18,031,946</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,690,546,662.66</x:t>
+    <x:t>18,046,128</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,772,968,028.48</x:t>
   </x:si>
   <x:si>
     <x:t>3.90%</x:t>
@@ -289,13 +292,13 @@
     <x:t>BBG0238L5JS9</x:t>
   </x:si>
   <x:si>
-    <x:t>18,491,130</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,637,204,960.60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.82%</x:t>
+    <x:t>18,505,642</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,689,980,121.12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.78%</x:t>
   </x:si>
   <x:si>
     <x:t>LRCX</x:t>
@@ -307,13 +310,13 @@
     <x:t>BBG000BNFLM9</x:t>
   </x:si>
   <x:si>
-    <x:t>10,442,696</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,480,140,300.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.60%</x:t>
+    <x:t>10,450,910</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,517,101,673.50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.54%</x:t>
   </x:si>
   <x:si>
     <x:t>CDNS</x:t>
@@ -325,13 +328,13 @@
     <x:t>BBG000C13CD9</x:t>
   </x:si>
   <x:si>
-    <x:t>4,494,819</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$1,448,095,837.23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.10%</x:t>
+    <x:t>4,498,355</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$1,543,295,633.40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.17%</x:t>
   </x:si>
   <x:si>
     <x:t>SNPS</x:t>
@@ -343,13 +346,13 @@
     <x:t>BBG000BSFRF3</x:t>
   </x:si>
   <x:si>
-    <x:t>3,166,329</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$1,438,558,254.57</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.09%</x:t>
+    <x:t>3,168,819</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$1,503,351,109.98</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.11%</x:t>
   </x:si>
   <x:si>
     <x:t>NXPI</x:t>
@@ -361,10 +364,10 @@
     <x:t>BBG000BND699</x:t>
   </x:si>
   <x:si>
-    <x:t>3,306,632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$812,869,344.56</x:t>
+    <x:t>3,309,232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$838,890,312.00</x:t>
   </x:si>
   <x:si>
     <x:t>1.18%</x:t>
@@ -379,13 +382,13 @@
     <x:t>BBG000C30L48</x:t>
   </x:si>
   <x:si>
-    <x:t>683,281</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$797,573,412.87</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.16%</x:t>
+    <x:t>683,819</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$828,713,407.91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.17%</x:t>
   </x:si>
   <x:si>
     <x:t>TER</x:t>
@@ -397,13 +400,31 @@
     <x:t>BBG000BV4DR6</x:t>
   </x:si>
   <x:si>
-    <x:t>2,425,663</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$749,529,867.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.09%</x:t>
+    <x:t>2,427,571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$785,756,181.28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.11%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Astera Labs Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG00TDKHW99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,448,832</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$702,055,646.08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.99%</x:t>
   </x:si>
   <x:si>
     <x:t>ARM</x:t>
@@ -415,31 +436,13 @@
     <x:t>BBG01J1GXZF0</x:t>
   </x:si>
   <x:si>
-    <x:t>3,012,788</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$672,906,199.80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.98%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Astera Labs Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG00TDKHW99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,446,908</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$634,997,095.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.92%</x:t>
+    <x:t>3,015,158</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$683,234,802.80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.96%</x:t>
   </x:si>
   <x:si>
     <x:t>STM</x:t>
@@ -451,13 +454,13 @@
     <x:t>BBG000BD4GX2</x:t>
   </x:si>
   <x:si>
-    <x:t>13,220,628</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$597,440,179.32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.87%</x:t>
+    <x:t>13,231,026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$644,086,345.68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.91%</x:t>
   </x:si>
   <x:si>
     <x:t>MCHP</x:t>
@@ -469,13 +472,13 @@
     <x:t>BBG000BHCP19</x:t>
   </x:si>
   <x:si>
-    <x:t>7,768,430</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$589,623,837.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.86%</x:t>
+    <x:t>7,774,540</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$623,284,871.80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.88%</x:t>
   </x:si>
   <x:si>
     <x:t>ON</x:t>
@@ -487,13 +490,13 @@
     <x:t>BBG000DV7MX4</x:t>
   </x:si>
   <x:si>
-    <x:t>4,785,144</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$354,387,764.64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.51%</x:t>
+    <x:t>4,788,908</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$376,743,392.36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.53%</x:t>
   </x:si>
   <x:si>
     <x:t>-USD CASH-</x:t>
@@ -502,13 +505,13 @@
     <x:t> </x:t>
   </x:si>
   <x:si>
-    <x:t>43,854,241</x:t>
+    <x:t>43,859,151</x:t>
   </x:si>
   <x:si>
     <x:t>Cash Bal</x:t>
   </x:si>
   <x:si>
-    <x:t>$43,854,241.01</x:t>
+    <x:t>$43,859,150.99</x:t>
   </x:si>
   <x:si>
     <x:t>0.06%</x:t>
@@ -520,7 +523,7 @@
     <x:t>Cash</x:t>
   </x:si>
   <x:si>
-    <x:t>$-12,335,974.05</x:t>
+    <x:t>$-13,579,851.57</x:t>
   </x:si>
   <x:si>
     <x:t>-0.02%</x:t>
@@ -897,7 +900,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9" ht="15" customHeight="1">
@@ -905,28 +908,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I11" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9" ht="15" customHeight="1">
@@ -934,28 +937,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I12" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9" ht="15" customHeight="1">
@@ -963,28 +966,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H13" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I13" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9" ht="15" customHeight="1">
@@ -992,28 +995,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H14" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I14" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9" ht="15" customHeight="1">
@@ -1021,28 +1024,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I15" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9" ht="15" customHeight="1">
@@ -1050,28 +1053,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I16" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9" ht="15" customHeight="1">
@@ -1079,28 +1082,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I17" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9" ht="15" customHeight="1">
@@ -1108,28 +1111,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I18" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9" ht="15" customHeight="1">
@@ -1137,28 +1140,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I19" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9" ht="15" customHeight="1">
@@ -1166,28 +1169,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I20" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9" ht="15" customHeight="1">
@@ -1195,28 +1198,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I21" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9" ht="15" customHeight="1">
@@ -1224,28 +1227,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I22" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9" ht="15" customHeight="1">
@@ -1253,28 +1256,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I23" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9" ht="15" customHeight="1">
@@ -1282,28 +1285,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I24" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9" ht="15" customHeight="1">
@@ -1311,28 +1314,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I25" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9" ht="15" customHeight="1">
@@ -1340,28 +1343,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I26" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9" ht="15" customHeight="1">
@@ -1369,28 +1372,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I27" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9" ht="15" customHeight="1">
@@ -1398,28 +1401,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I28" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9" ht="15" customHeight="1">
@@ -1427,28 +1430,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I29" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9" ht="15" customHeight="1">
@@ -1459,7 +1462,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
         <x:v>17</x:v>
@@ -1468,21 +1471,21 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I30" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9" ht="15" customHeight="1">
       <x:c r="A31" s="2" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
         <x:v>1</x:v>
